--- a/data/trans_camb/IP16A05-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP16A05-Provincia-trans_camb.xlsx
@@ -614,7 +614,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 39,17</t>
+          <t>-3,16; 42,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-25,76; 3,01</t>
+          <t>-27,51; 3,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,89; 34,85</t>
+          <t>-12,84; 31,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-26,22; 14,67</t>
+          <t>-28,83; 13,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-24,54; 20,02</t>
+          <t>-24,46; 19,96</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-37,18; -0,18</t>
+          <t>-38,66; 0,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-11,46; 23,33</t>
+          <t>-10,11; 21,01</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-17,32; 10,05</t>
+          <t>-17,02; 8,36</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-16,34; 14,21</t>
+          <t>-17,51; 14,98</t>
         </is>
       </c>
     </row>
@@ -783,7 +783,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-45,8; —</t>
+          <t>-54,33; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-84,05; 426,96</t>
+          <t>-82,05; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -813,24 +813,24 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-57,11; 510,51</t>
+          <t>-54,55; 404,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-81,69; 206,63</t>
+          <t>-80,29; 171,56</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-86,21; 320,03</t>
+          <t>-86,36; 505,57</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,94; 13,88</t>
+          <t>-11,76; 14,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,55; 10,64</t>
+          <t>-14,22; 9,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-20,74; 1,54</t>
+          <t>-19,17; 1,77</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 18,41</t>
+          <t>-4,04; 19,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12,69; 48,61</t>
+          <t>12,97; 48,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-12,09; 5,06</t>
+          <t>-10,06; 5,26</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,31; 13,09</t>
+          <t>-3,28; 13,89</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,6; 22,79</t>
+          <t>2,89; 23,72</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-10,75; 1,79</t>
+          <t>-11,39; 2,06</t>
         </is>
       </c>
     </row>
@@ -1029,12 +1029,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-61,05; 723,42</t>
+          <t>-53,33; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 1292,83</t>
+          <t>5,96; —</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,48; 43,34</t>
+          <t>0,86; 46,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 47,41</t>
+          <t>-3,28; 48,41</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-23,95; 4,44</t>
+          <t>-23,9; 4,39</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,87; 28,29</t>
+          <t>-5,67; 28,19</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-12,09; 24,65</t>
+          <t>-12,03; 24,32</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-23,96; 6,09</t>
+          <t>-20,68; 5,87</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,39; 30,78</t>
+          <t>2,47; 31,34</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 29,64</t>
+          <t>-3,13; 28,74</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-15,31; 3,2</t>
+          <t>-16,75; 3,15</t>
         </is>
       </c>
     </row>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-6,19; —</t>
+          <t>-18,91; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,49; 24,88</t>
+          <t>-5,68; 24,51</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 26,45</t>
+          <t>-2,03; 28,45</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-23,45; 0,0</t>
+          <t>-23,42; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-18,39; 27,37</t>
+          <t>-18,71; 26,44</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-29,57; 6,99</t>
+          <t>-27,53; 8,7</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-26,43; 26,3</t>
+          <t>-25,98; 25,95</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-8,54; 20,2</t>
+          <t>-8,71; 19,54</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-11,14; 13,63</t>
+          <t>-9,77; 12,67</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-16,84; 11,14</t>
+          <t>-16,56; 10,47</t>
         </is>
       </c>
     </row>
@@ -1446,12 +1446,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-79,15; 422,29</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 179,26</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1461,12 +1461,12 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-57,41; 499,07</t>
+          <t>-55,62; 526,17</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-62,47; 348,04</t>
+          <t>-60,8; 265,14</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>10,54; 54,29</t>
+          <t>10,43; 54,11</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,7</t>
+          <t>0,0; 52,04</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,07</t>
+          <t>0,0; 40,46</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,9</t>
+          <t>0,0; 23,32</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1571,17 +1571,17 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,03; 31,62</t>
+          <t>8,02; 33,43</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,36</t>
+          <t>0,0; 32,23</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,63</t>
+          <t>0,0; 17,54</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1694,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-5,85; 33,98</t>
+          <t>-10,21; 38,6</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-11,51; 26,06</t>
+          <t>-11,66; 26,96</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-11,57; 23,14</t>
+          <t>-11,51; 25,3</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-21,73; 18,06</t>
+          <t>-23,3; 18,77</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-23,67; 30,5</t>
+          <t>-23,14; 30,0</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-25,24; 13,28</t>
+          <t>-23,95; 12,34</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-9,78; 18,33</t>
+          <t>-10,41; 17,16</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-12,95; 18,83</t>
+          <t>-12,16; 19,33</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-14,43; 10,43</t>
+          <t>-14,68; 12,09</t>
         </is>
       </c>
     </row>
@@ -1893,7 +1893,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-73,84; 1081,57</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-24,82; 9,09</t>
+          <t>-23,3; 9,92</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-32,52; -6,15</t>
+          <t>-32,25; -6,18</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-13,74; 24,6</t>
+          <t>-12,49; 24,8</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-8,05; 18,11</t>
+          <t>-8,12; 16,77</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-16,2; 0,0</t>
+          <t>-16,51; 0,0</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-6,9; 15,36</t>
+          <t>-7,98; 14,92</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-10,04; 10,09</t>
+          <t>-10,07; 11,63</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-19,58; -4,49</t>
+          <t>-19,04; -4,35</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-4,31; 15,54</t>
+          <t>-6,08; 14,91</t>
         </is>
       </c>
     </row>
@@ -2079,7 +2079,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-90,65; 153,49</t>
+          <t>-89,85; 186,41</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-51,56; 341,23</t>
+          <t>-52,06; 401,22</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -2104,12 +2104,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-68,74; 218,12</t>
+          <t>-66,02; 264,54</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-35,4; 298,07</t>
+          <t>-36,41; 276,13</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-8,01; 26,71</t>
+          <t>-8,89; 26,55</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-8,32; 25,16</t>
+          <t>-9,09; 24,95</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-24,9; -4,87</t>
+          <t>-24,69; -4,9</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-14,0; 19,26</t>
+          <t>-14,46; 18,73</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-17,34; 8,52</t>
+          <t>-17,93; 8,82</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-20,09; 9,3</t>
+          <t>-19,82; 11,13</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-6,41; 14,58</t>
+          <t>-7,03; 16,78</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-9,72; 10,41</t>
+          <t>-9,7; 11,21</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-18,47; 1,58</t>
+          <t>-17,84; 1,07</t>
         </is>
       </c>
     </row>
@@ -2295,12 +2295,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-49,58; 523,2</t>
+          <t>-58,1; 424,55</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-52,14; 423,04</t>
+          <t>-57,2; 464,91</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -2310,32 +2310,32 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-75,02; 222,46</t>
+          <t>-81,32; 238,43</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-87,05; 118,99</t>
+          <t>-100,0; 124,32</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 183,62</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-40,48; 147,77</t>
+          <t>-42,71; 179,6</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-53,52; 108,19</t>
+          <t>-56,39; 119,87</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 46,36</t>
+          <t>-100,0; 144,94</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>2,11; 16,15</t>
+          <t>2,5; 15,44</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 8,48</t>
+          <t>-3,03; 8,47</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-6,24; 6,73</t>
+          <t>-6,73; 5,75</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 8,73</t>
+          <t>-2,53; 8,82</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 9,33</t>
+          <t>-3,49; 9,57</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-9,75; 0,54</t>
+          <t>-9,99; -0,26</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>1,44; 10,34</t>
+          <t>1,26; 10,12</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 7,19</t>
+          <t>-1,55; 7,01</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 1,67</t>
+          <t>-6,83; 1,1</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>16,17; 285,28</t>
+          <t>17,39; 254,07</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-30,36; 135,96</t>
+          <t>-30,02; 137,43</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-53,45; 105,53</t>
+          <t>-56,81; 95,67</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-24,3; 118,08</t>
+          <t>-22,38; 119,51</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-28,1; 122,12</t>
+          <t>-29,68; 129,07</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-74,9; 10,21</t>
+          <t>-73,84; 5,15</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>12,21; 140,88</t>
+          <t>9,42; 126,76</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-15,71; 93,45</t>
+          <t>-13,15; 90,77</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-55,13; 20,49</t>
+          <t>-57,69; 16,73</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A05-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP16A05-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 42,3</t>
+          <t>-5,34; 40,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-27,51; 3,19</t>
+          <t>-25,74; 2,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-12,84; 31,98</t>
+          <t>-11,76; 36,47</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-28,83; 13,29</t>
+          <t>-29,07; 15,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-24,46; 19,96</t>
+          <t>-24,28; 21,02</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-38,66; 0,0</t>
+          <t>-38,21; 0,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-10,11; 21,01</t>
+          <t>-11,51; 20,23</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-17,02; 8,36</t>
+          <t>-16,17; 11,03</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-17,51; 14,98</t>
+          <t>-17,21; 14,38</t>
         </is>
       </c>
     </row>
@@ -783,7 +783,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-54,33; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-90,55; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-82,05; —</t>
+          <t>-82,14; 524,36</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-54,55; 404,27</t>
+          <t>-54,14; 373,98</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-80,29; 171,56</t>
+          <t>-77,65; 258,77</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-86,36; 505,57</t>
+          <t>-86,68; 445,6</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,76; 14,32</t>
+          <t>-12,58; 14,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-14,22; 9,11</t>
+          <t>-13,98; 10,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-19,17; 1,77</t>
+          <t>-19,88; 1,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 19,15</t>
+          <t>-3,8; 21,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12,97; 48,02</t>
+          <t>13,14; 46,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-10,06; 5,26</t>
+          <t>-11,0; 5,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 13,89</t>
+          <t>-4,36; 13,26</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,89; 23,72</t>
+          <t>2,79; 22,87</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-11,39; 2,06</t>
+          <t>-11,07; 1,56</t>
         </is>
       </c>
     </row>
@@ -1029,12 +1029,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-53,33; —</t>
+          <t>-59,42; 814,07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,96; —</t>
+          <t>4,63; 1413,53</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,86; 46,21</t>
+          <t>1,54; 46,89</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 48,41</t>
+          <t>-3,08; 47,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-23,9; 4,39</t>
+          <t>-21,53; 4,24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 28,19</t>
+          <t>-6,0; 28,3</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-12,03; 24,32</t>
+          <t>-12,02; 26,37</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-20,68; 5,87</t>
+          <t>-23,24; 6,07</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,47; 31,34</t>
+          <t>4,51; 31,51</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 28,74</t>
+          <t>-5,1; 28,2</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-16,75; 3,15</t>
+          <t>-14,64; 3,16</t>
         </is>
       </c>
     </row>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-18,91; —</t>
+          <t>7,02; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,68; 24,51</t>
+          <t>-6,37; 24,37</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 28,45</t>
+          <t>-2,58; 28,8</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-23,42; 0,0</t>
+          <t>-23,75; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-18,71; 26,44</t>
+          <t>-19,7; 28,53</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-27,53; 8,7</t>
+          <t>-29,34; 6,2</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-25,98; 25,95</t>
+          <t>-26,16; 25,93</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-8,71; 19,54</t>
+          <t>-7,99; 20,87</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-9,77; 12,67</t>
+          <t>-10,89; 12,77</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-16,56; 10,47</t>
+          <t>-16,43; 10,16</t>
         </is>
       </c>
     </row>
@@ -1446,12 +1446,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-79,15; 422,29</t>
+          <t>-80,11; 463,81</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 142,3</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1461,12 +1461,12 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-55,62; 526,17</t>
+          <t>-54,57; 416,89</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-60,8; 265,14</t>
+          <t>-60,96; 274,33</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>10,43; 54,11</t>
+          <t>10,45; 53,15</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,04</t>
+          <t>0,0; 52,13</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,46</t>
+          <t>0,0; 38,6</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,32</t>
+          <t>0,0; 23,42</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1571,17 +1571,17 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,02; 33,43</t>
+          <t>8,07; 35,17</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,23</t>
+          <t>0,0; 33,12</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,54</t>
+          <t>0,0; 20,76</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-10,21; 38,6</t>
+          <t>-10,67; 29,74</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-11,66; 26,96</t>
+          <t>-11,6; 25,87</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-11,51; 25,3</t>
+          <t>-11,54; 22,68</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-23,3; 18,77</t>
+          <t>-19,98; 19,05</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-23,14; 30,0</t>
+          <t>-23,14; 30,77</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-23,95; 12,34</t>
+          <t>-29,1; 12,66</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-10,41; 17,16</t>
+          <t>-11,49; 17,59</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-12,16; 19,33</t>
+          <t>-12,57; 20,08</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-14,68; 12,09</t>
+          <t>-14,08; 10,83</t>
         </is>
       </c>
     </row>
@@ -1893,7 +1893,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-73,84; 1081,57</t>
+          <t>-80,55; —</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-23,3; 9,92</t>
+          <t>-22,06; 11,54</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-32,25; -6,18</t>
+          <t>-32,48; -6,35</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-12,49; 24,8</t>
+          <t>-11,75; 24,82</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-8,12; 16,77</t>
+          <t>-6,98; 18,74</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-16,51; 0,0</t>
+          <t>-19,07; 0,0</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-7,98; 14,92</t>
+          <t>-6,9; 16,1</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-10,07; 11,63</t>
+          <t>-9,88; 9,79</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-19,04; -4,35</t>
+          <t>-19,0; -4,36</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-6,08; 14,91</t>
+          <t>-4,32; 15,82</t>
         </is>
       </c>
     </row>
@@ -2079,7 +2079,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-89,85; 186,41</t>
+          <t>-87,16; 231,92</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-52,06; 401,22</t>
+          <t>-49,38; 367,29</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -2104,12 +2104,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-66,02; 264,54</t>
+          <t>-68,28; 204,65</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-36,41; 276,13</t>
+          <t>-31,51; 308,41</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-8,89; 26,55</t>
+          <t>-6,4; 27,56</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-9,09; 24,95</t>
+          <t>-7,86; 25,34</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-24,69; -4,9</t>
+          <t>-24,77; -4,93</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-14,46; 18,73</t>
+          <t>-13,01; 19,85</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-17,93; 8,82</t>
+          <t>-17,71; 9,82</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-19,82; 11,13</t>
+          <t>-19,04; 12,9</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-7,03; 16,78</t>
+          <t>-7,13; 16,17</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-9,7; 11,21</t>
+          <t>-10,37; 11,6</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-17,84; 1,07</t>
+          <t>-17,94; 2,41</t>
         </is>
       </c>
     </row>
@@ -2295,12 +2295,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-58,1; 424,55</t>
+          <t>-48,12; 491,5</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-57,2; 464,91</t>
+          <t>-51,29; 464,32</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -2310,32 +2310,32 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-81,32; 238,43</t>
+          <t>-76,21; 235,59</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 124,32</t>
+          <t>-86,1; 139,63</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 183,62</t>
+          <t>-100,0; 222,4</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-42,71; 179,6</t>
+          <t>-44,02; 173,27</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-56,39; 119,87</t>
+          <t>-56,65; 137,14</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 144,94</t>
+          <t>-100,0; 69,17</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>2,5; 15,44</t>
+          <t>2,68; 15,47</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 8,47</t>
+          <t>-3,51; 8,14</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-6,73; 5,75</t>
+          <t>-6,47; 5,85</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 8,82</t>
+          <t>-2,99; 9,2</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 9,57</t>
+          <t>-3,26; 9,41</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-9,99; -0,26</t>
+          <t>-10,03; -0,02</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>1,26; 10,12</t>
+          <t>0,93; 10,31</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 7,01</t>
+          <t>-1,34; 7,08</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-6,83; 1,1</t>
+          <t>-6,87; 1,12</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>17,39; 254,07</t>
+          <t>19,25; 250,74</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-30,02; 137,43</t>
+          <t>-31,27; 129,42</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-56,81; 95,67</t>
+          <t>-59,12; 90,58</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-22,38; 119,51</t>
+          <t>-24,43; 117,09</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-29,68; 129,07</t>
+          <t>-27,93; 122,51</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-73,84; 5,15</t>
+          <t>-75,81; 3,34</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>9,42; 126,76</t>
+          <t>7,04; 139,79</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-13,15; 90,77</t>
+          <t>-13,16; 88,27</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-57,69; 16,73</t>
+          <t>-57,68; 17,04</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A05-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP16A05-Provincia-trans_camb.xlsx
@@ -523,20 +523,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos antibióticos</t>
+          <t>Menores que consumieron medicamentos antibióticos</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-5,16</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,32</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-14,99</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>18,24</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-6,64</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>6,36</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-5,16</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,32</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-14,85</t>
+          <t>0,03</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-3,25</t>
+          <t>-7,41</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 40,17</t>
+          <t>-26,22; 14,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-25,74; 2,98</t>
+          <t>-24,54; 20,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,76; 36,47</t>
+          <t>-37,32; -0,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-29,07; 15,79</t>
+          <t>-3,75; 39,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-24,28; 21,02</t>
+          <t>-25,76; 3,01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-38,21; 0,0</t>
+          <t>-18,3; 13,83</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-11,51; 20,23</t>
+          <t>-11,46; 23,33</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-16,17; 11,03</t>
+          <t>-17,32; 10,05</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-17,21; 14,38</t>
+          <t>-22,13; 2,27</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-30,79%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1,91%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-89,49%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>190,93%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-69,52%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>66,54%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-30,79%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1,91%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-88,63%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-24,54%</t>
+          <t>-55,99%</t>
         </is>
       </c>
     </row>
@@ -788,22 +788,22 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-84,05; 426,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-90,55; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>-45,8; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-82,14; 524,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-54,14; 373,98</t>
+          <t>-57,11; 510,51</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-77,65; 258,77</t>
+          <t>-81,69; 206,63</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-86,68; 445,6</t>
+          <t>-90,89; 64,97</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>7,36</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>29,03</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-0,36</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>1,44</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-0,54</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-5,77</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>7,36</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>29,03</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-5,29</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-2,85</t>
+          <t>-2,63</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,58; 14,19</t>
+          <t>-4,35; 18,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,98; 10,21</t>
+          <t>12,69; 48,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-19,88; 1,29</t>
+          <t>-12,68; 4,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 21,13</t>
+          <t>-11,94; 13,88</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13,14; 46,42</t>
+          <t>-13,55; 10,64</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-11,0; 5,28</t>
+          <t>-19,22; 1,92</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 13,26</t>
+          <t>-4,31; 13,09</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,79; 22,87</t>
+          <t>2,6; 22,79</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-11,07; 1,56</t>
+          <t>-9,82; 1,96</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>227,5%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>897,69%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-11,19%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>20,4%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-7,67%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-81,69%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>227,5%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>897,69%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>-74,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-57,19%</t>
+          <t>-52,83%</t>
         </is>
       </c>
     </row>
@@ -1029,12 +1029,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-59,42; 814,07</t>
+          <t>-61,05; 723,42</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,63; 1413,53</t>
+          <t>-2,15; 1292,83</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>12,62</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1,95</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-2,58</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>23,22</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>17,56</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-3,55</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>12,62</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1,95</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-2,96</t>
+          <t>-3,7</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-3,22</t>
+          <t>-3,12</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,54; 46,89</t>
+          <t>-5,87; 28,29</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 47,38</t>
+          <t>-12,09; 24,65</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-21,53; 4,24</t>
+          <t>-23,07; 6,87</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,0; 28,3</t>
+          <t>1,48; 43,34</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-12,02; 26,37</t>
+          <t>-3,55; 47,41</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-23,24; 6,07</t>
+          <t>-24,2; 4,14</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,51; 31,51</t>
+          <t>4,39; 30,78</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,1; 28,2</t>
+          <t>-3,85; 29,64</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-14,64; 3,16</t>
+          <t>-15,13; 3,46</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>209,7%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>32,45%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-42,83%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>403,36%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>305,07%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-61,61%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>209,7%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>32,45%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-49,17%</t>
+          <t>-64,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-54,76%</t>
+          <t>-53,06%</t>
         </is>
       </c>
     </row>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,02; —</t>
+          <t>-6,19; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1272,34 +1272,34 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3,0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-8,47</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-5,91</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>8,67</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>13,23</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>-4,78</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3,0</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-8,47</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-6,07</t>
-        </is>
-      </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
           <t>5,44</t>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-5,77</t>
+          <t>-5,8</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,37; 24,37</t>
+          <t>-18,39; 27,37</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 28,8</t>
+          <t>-29,57; 6,99</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-23,75; 0,0</t>
+          <t>-26,38; 26,95</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-19,7; 28,53</t>
+          <t>-6,49; 24,88</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-29,34; 6,2</t>
+          <t>-4,02; 26,45</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-26,16; 25,93</t>
+          <t>-23,45; 0,0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-7,99; 20,87</t>
+          <t>-8,54; 20,2</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-10,89; 12,77</t>
+          <t>-11,14; 13,63</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-16,43; 10,16</t>
+          <t>-16,94; 10,71</t>
         </is>
       </c>
     </row>
@@ -1378,34 +1378,34 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>17,72%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-49,98%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-34,89%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>181,45%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>277,05%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>17,72%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-49,98%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>-35,85%</t>
-        </is>
-      </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
           <t>50,0%</t>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-53,09%</t>
+          <t>-53,32%</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 179,26</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1446,12 +1446,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-80,11; 463,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 142,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1461,12 +1461,12 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-54,57; 416,89</t>
+          <t>-57,41; 499,07</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-60,96; 274,33</t>
+          <t>-62,47; 348,04</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>5,67</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>27,39</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>18,34</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>13,6</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>5,67</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>14,09</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>5,92</t>
+          <t>6,54</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>10,45; 53,15</t>
+          <t>0,0; 23,9</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,13</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,6</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,42</t>
+          <t>10,54; 54,29</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 53,7</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 41,23</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,07; 35,17</t>
+          <t>6,03; 31,62</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,12</t>
+          <t>0,0; 32,36</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,76</t>
+          <t>0,0; 21,3</t>
         </is>
       </c>
     </row>
@@ -1599,27 +1599,27 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>0,43</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-0,62</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>-5,59</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>7,76</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>2,38</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>1,67</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>0,43</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>-0,62</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-5,74</t>
+          <t>1,73</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-2,0</t>
+          <t>-1,83</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-10,67; 29,74</t>
+          <t>-21,73; 18,06</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-11,6; 25,87</t>
+          <t>-23,67; 30,5</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-11,54; 22,68</t>
+          <t>-23,78; 16,83</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-19,98; 19,05</t>
+          <t>-5,85; 33,98</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-23,14; 30,77</t>
+          <t>-11,51; 26,06</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-29,1; 12,66</t>
+          <t>-11,52; 23,9</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-11,49; 17,59</t>
+          <t>-9,78; 18,33</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-12,57; 20,08</t>
+          <t>-12,95; 18,83</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-14,08; 10,83</t>
+          <t>-14,1; 11,09</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>3,64%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>-5,23%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>-47,15%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>135,51%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>41,52%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>29,1%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>3,64%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>-5,23%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-48,41%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-23,28%</t>
+          <t>-21,34%</t>
         </is>
       </c>
     </row>
@@ -1893,7 +1893,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-80,55; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>4,1</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-5,45</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>4,82</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>-5,02</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>-16,16</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>8,27</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>4,1</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>-5,45</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,55</t>
+          <t>7,34</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>5,56</t>
+          <t>5,57</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-22,06; 11,54</t>
+          <t>-8,05; 18,11</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-32,48; -6,35</t>
+          <t>-16,2; 0,0</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-11,75; 24,82</t>
+          <t>-6,87; 15,86</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-6,98; 18,74</t>
+          <t>-24,82; 9,09</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-19,07; 0,0</t>
+          <t>-32,52; -6,15</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-6,9; 16,1</t>
+          <t>-14,97; 23,83</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-9,88; 9,79</t>
+          <t>-10,04; 10,09</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-19,0; -4,36</t>
+          <t>-19,58; -4,49</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 15,82</t>
+          <t>-4,22; 15,5</t>
         </is>
       </c>
     </row>
@@ -2026,47 +2026,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>75,22%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>88,54%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>-31,07%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>51,21%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>75,22%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>45,45%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>1,15%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>83,6%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>54,25%</t>
+          <t>54,35%</t>
         </is>
       </c>
     </row>
@@ -2079,7 +2079,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-87,16; 231,92</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2089,12 +2089,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-49,38; 367,29</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-90,65; 153,49</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -2104,12 +2104,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-52,8; 330,25</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-68,28; 204,65</t>
+          <t>-68,74; 218,12</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-31,51; 308,41</t>
+          <t>-35,31; 300,01</t>
         </is>
       </c>
     </row>
@@ -2136,34 +2136,34 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>-0,02</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>-5,54</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>-9,78</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>8,25</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>7,68</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>-12,44</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>-0,02</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>-5,54</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>-8,55</t>
-        </is>
-      </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
           <t>3,84</t>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-10,18</t>
+          <t>-10,83</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-6,4; 27,56</t>
+          <t>-14,0; 19,26</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-7,86; 25,34</t>
+          <t>-17,34; 8,52</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-24,77; -4,93</t>
+          <t>-21,0; 5,51</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-13,01; 19,85</t>
+          <t>-8,01; 26,71</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-17,71; 9,82</t>
+          <t>-8,32; 25,16</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-19,04; 12,9</t>
+          <t>-24,9; -4,87</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-7,13; 16,17</t>
+          <t>-6,41; 14,58</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-10,37; 11,6</t>
+          <t>-9,72; 10,41</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-17,94; 2,41</t>
+          <t>-18,86; -0,93</t>
         </is>
       </c>
     </row>
@@ -2242,34 +2242,34 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>-0,11%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>-37,65%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>-66,42%</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>66,36%</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>61,76%</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>-0,11%</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>-37,65%</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>-58,07%</t>
-        </is>
-      </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
           <t>27,81%</t>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-73,62%</t>
+          <t>-78,35%</t>
         </is>
       </c>
     </row>
@@ -2295,12 +2295,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-48,12; 491,5</t>
+          <t>-75,02; 222,46</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-51,29; 464,32</t>
+          <t>-87,05; 118,99</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -2310,32 +2310,32 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-76,21; 235,59</t>
+          <t>-49,58; 523,2</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-86,1; 139,63</t>
+          <t>-52,14; 423,04</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 222,4</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-44,02; 173,27</t>
+          <t>-40,48; 147,77</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-56,65; 137,14</t>
+          <t>-53,52; 108,19</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 69,17</t>
+          <t>-100,0; 23,04</t>
         </is>
       </c>
     </row>
@@ -2352,47 +2352,47 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>2,75</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>2,82</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>-4,79</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>8,95</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>2,78</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>-0,45</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>-0,57</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>5,73</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
         <is>
           <t>2,75</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>2,82</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>-4,82</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>5,73</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>2,75</t>
-        </is>
-      </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-2,7</t>
+          <t>-2,83</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>2,68; 15,47</t>
+          <t>-2,92; 8,73</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 8,14</t>
+          <t>-3,61; 9,33</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-6,47; 5,85</t>
+          <t>-9,84; 0,55</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 9,2</t>
+          <t>2,11; 16,15</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 9,41</t>
+          <t>-3,3; 8,48</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-10,03; -0,02</t>
+          <t>-5,9; 4,75</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,93; 10,31</t>
+          <t>1,44; 10,34</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 7,08</t>
+          <t>-1,81; 7,19</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-6,87; 1,12</t>
+          <t>-6,46; 0,75</t>
         </is>
       </c>
     </row>
@@ -2458,32 +2458,32 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>26,99%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>27,68%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>-46,91%</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>100,58%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>31,27%</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>-5,1%</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>26,99%</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>27,68%</t>
-        </is>
-      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-47,29%</t>
+          <t>-6,43%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-28,17%</t>
+          <t>-29,46%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>19,25; 250,74</t>
+          <t>-24,3; 118,08</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-31,27; 129,42</t>
+          <t>-28,1; 122,12</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-59,12; 90,58</t>
+          <t>-74,88; 12,87</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-24,43; 117,09</t>
+          <t>16,17; 285,28</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-27,93; 122,51</t>
+          <t>-30,36; 135,96</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-75,81; 3,34</t>
+          <t>-50,1; 81,93</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>7,04; 139,79</t>
+          <t>12,21; 140,88</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-13,16; 88,27</t>
+          <t>-15,71; 93,45</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-57,68; 17,04</t>
+          <t>-55,67; 12,39</t>
         </is>
       </c>
     </row>
